--- a/naver-place-crawler/results_health/파주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/파주_헬스장.xlsx
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>파이 피트니스 스타필드점 헬스PT스피닝</t>
+          <t>파이 피트니스 다율점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>pifitness@naver.com</t>
+          <t>pifitness02@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1350-3458</t>
+          <t>0507-1436-5392</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 파주시 경의로1240번길 14-11 8층</t>
+          <t>경기 파주시 해올2길 8 1006~1009호(다율동)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pifitness?tab=1&amp;trackingCode=blog_feed_mobile</t>
+          <t>https://open.kakao.com/o/sWflSZei</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wl490ee</t>
+          <t>https://talk.naver.com/ct/whg35h5</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>480</v>
+        <v>30</v>
       </c>
       <c r="Q2" t="n">
-        <v>2323</v>
+        <v>72</v>
       </c>
       <c r="R2" t="n">
-        <v>2803</v>
+        <v>102</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1448948729</t>
+          <t>2076933270</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1448948729</t>
+          <t>https://m.place.naver.com/place/2076933270</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,34 +662,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>디클리셰 24시 GTX점 헬스 기구필라테스 스피닝 GX</t>
+          <t>파이 피트니스 스타필드점 헬스PT스피닝</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>decliche32@naver.com</t>
+          <t>pifitness@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1425-4121</t>
+          <t>0507-1350-3458</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 파주시 초롱꽃로 141 B동 7층</t>
+          <t>경기 파주시 경의로1240번길 14-11 8층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://decliche.co.kr/default/</t>
+          <t>https://blog.naver.com/pifitness?tab=1&amp;trackingCode=blog_feed_mobile</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -704,13 +704,17 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wl490ee</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>693</v>
+        <v>481</v>
       </c>
       <c r="Q3" t="n">
-        <v>1143</v>
+        <v>2323</v>
       </c>
       <c r="R3" t="n">
-        <v>1836</v>
+        <v>2804</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1628652531</t>
+          <t>1448948729</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1628652531</t>
+          <t>https://m.place.naver.com/place/1448948729</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -756,24 +760,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>디클리셰 24시 스타필드점 헬스 기구필라테스 GX</t>
+          <t>디클리셰 24시 GTX점 헬스 기구필라테스 스피닝 GX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>decliche22@naver.com</t>
+          <t>decliche32@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1415-4121</t>
+          <t>0507-1425-4121</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 파주시 금바위로 42 운정법조타운 3층</t>
+          <t>경기 파주시 초롱꽃로 141 B동 7층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -803,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4fj83</t>
+          <t>https://talk.naver.com/ct/w5t0nq</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -817,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>890</v>
+        <v>693</v>
       </c>
       <c r="Q4" t="n">
-        <v>541</v>
+        <v>1186</v>
       </c>
       <c r="R4" t="n">
-        <v>1431</v>
+        <v>1879</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1320392834</t>
+          <t>1628652531</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1320392834</t>
+          <t>https://m.place.naver.com/place/1628652531</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -854,34 +858,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>F45 운정</t>
+          <t>디클리셰 24시 스타필드점 헬스 기구필라테스 GX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>f45unjeong@naver.com</t>
+          <t>decliche22@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1391-6365</t>
+          <t>0507-1415-4121</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 파주시 청암로17번길 21 월드타워5차 701호 702호</t>
+          <t>경기 파주시 금바위로 42 운정법조타운 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/f45_unjeong</t>
+          <t>https://decliche.co.kr/default/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -891,7 +895,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -901,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5zxi6</t>
+          <t>https://talk.naver.com/ct/w4fj83</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -915,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>132</v>
+        <v>890</v>
       </c>
       <c r="Q5" t="n">
-        <v>420</v>
+        <v>551</v>
       </c>
       <c r="R5" t="n">
-        <v>552</v>
+        <v>1441</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1564837926</t>
+          <t>1320392834</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1564837926</t>
+          <t>https://m.place.naver.com/place/1320392834</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -952,34 +956,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>온짐 헬스&amp;PT 야당점</t>
+          <t>F45 운정</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>on-gym@naver.com</t>
+          <t>f45unjeong@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1437-7707</t>
+          <t>0507-1391-6365</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로 1068 삼융프라자 4층 403~4호</t>
+          <t>경기 파주시 청암로17번길 21 월드타워5차 701호 702호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_IVxesn/chat</t>
+          <t>https://www.instagram.com/f45_unjeong</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -994,13 +998,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5zxi6</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1009,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>201</v>
+        <v>132</v>
       </c>
       <c r="Q6" t="n">
-        <v>892</v>
+        <v>420</v>
       </c>
       <c r="R6" t="n">
-        <v>1093</v>
+        <v>552</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1024,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1537889737</t>
+          <t>1564837926</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1537889737</t>
+          <t>https://m.place.naver.com/place/1564837926</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1046,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>머스타드피트니스 운정점</t>
+          <t>온짐 헬스&amp;PT 야당점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mustard_fitness3@naver.com</t>
+          <t>on-gym@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1403-6882</t>
+          <t>0507-1437-7707</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 파주시 와석순환로 86 지앤지프라자 5층</t>
+          <t>경기 파주시 경의로 1068 삼융프라자 4층 403~4호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://www.mustard-fitness.com</t>
+          <t>https://pf.kakao.com/_IVxesn/chat</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1083,18 +1091,22 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wphkbsb</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1103,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1042</v>
+        <v>201</v>
       </c>
       <c r="Q7" t="n">
-        <v>124</v>
+        <v>899</v>
       </c>
       <c r="R7" t="n">
-        <v>1166</v>
+        <v>1100</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1118,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>584588992</t>
+          <t>1537889737</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/584588992</t>
+          <t>https://m.place.naver.com/place/1537889737</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1140,34 +1152,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>다다짐 헬스&amp;PT 운정본점</t>
+          <t>머스타드피트니스 운정점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dadagym@naver.com</t>
+          <t>mustard_fitness3@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1304-1646</t>
+          <t>0507-1403-6882</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 파주시 미래로602번길 11 701호,702호</t>
+          <t>경기 파주시 와석순환로 86 지앤지프라자 5층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dadagym/224242550028</t>
+          <t>http://www.mustard-fitness.com</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1187,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4v2ogs</t>
+          <t>https://talk.naver.com/ct/w5itt3</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1201,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>59</v>
+        <v>1042</v>
       </c>
       <c r="Q8" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="R8" t="n">
-        <v>129</v>
+        <v>1166</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1216,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1236035000</t>
+          <t>584588992</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1236035000</t>
+          <t>https://m.place.naver.com/place/584588992</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1238,44 +1250,44 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1퍼센트짐 금릉점 헬스&amp;PT</t>
+          <t>다다짐 헬스&amp;PT 운정본점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1percentgym2@naver.com</t>
+          <t>dadagym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1386-4598</t>
+          <t>0507-1304-1646</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 파주시 금빛로 4-1 3층 301호,302호</t>
+          <t>경기 파주시 미래로602번길 11 701호,702호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/1113882</t>
+          <t>https://blog.naver.com/dadagym/224242550028</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1285,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5yr9z</t>
+          <t>https://talk.naver.com/ct/w4v2ogs</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1299,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>387</v>
+        <v>59</v>
       </c>
       <c r="Q9" t="n">
-        <v>267</v>
+        <v>70</v>
       </c>
       <c r="R9" t="n">
-        <v>654</v>
+        <v>129</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1314,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1714420485</t>
+          <t>1236035000</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1714420485</t>
+          <t>https://m.place.naver.com/place/1236035000</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1353,7 +1365,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로 1114 505호</t>
+          <t>경기 파주시 경의로 1114 505호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1378,10 +1390,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wjtwmo7</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1393,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q10" t="n">
         <v>28</v>
       </c>
       <c r="R10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/파주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/파주_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>파이 피트니스 다율점</t>
+          <t>짐원휘트니스 운정9호점 헬스PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>pifitness02@naver.com</t>
+          <t>gymone9@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1436-5392</t>
+          <t>0507-1395-9681</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 파주시 해올2길 8 1006~1009호(다율동)</t>
+          <t>경기도 파주시 경의로 1246 유은타워 8차 10층 짐원휘트니스 운정9호점</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sWflSZei</t>
+          <t>https://www.instagram.com/gymone_fitness9?igsh=aDY4YjNvYmt5aXFx</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,17 +606,13 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/whg35h5</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="Q2" t="n">
-        <v>72</v>
+        <v>155</v>
       </c>
       <c r="R2" t="n">
-        <v>102</v>
+        <v>213</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2076933270</t>
+          <t>1825844752</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2076933270</t>
+          <t>https://m.place.naver.com/place/1825844752</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -657,39 +653,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>파이 피트니스 스타필드점 헬스PT스피닝</t>
+          <t>애블바디PT 해오름마을 1호점 헬스PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pifitness@naver.com</t>
+          <t>every_body_pt@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1350-3458</t>
+          <t>0507-1362-5290</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 파주시 경의로1240번길 14-11 8층</t>
+          <t>경기도 파주시 해올2길 16 공감빌딩 6층 애블바디 P.T샵</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pifitness?tab=1&amp;trackingCode=blog_feed_mobile</t>
+          <t>https://smartstore.naver.com/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -699,37 +695,33 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wl490ee</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>481</v>
+        <v>148</v>
       </c>
       <c r="Q3" t="n">
-        <v>2323</v>
+        <v>276</v>
       </c>
       <c r="R3" t="n">
-        <v>2804</v>
+        <v>424</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1448948729</t>
+          <t>1831911897</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1448948729</t>
+          <t>https://m.place.naver.com/place/1831911897</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -755,39 +747,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>디클리셰 24시 GTX점 헬스 기구필라테스 스피닝 GX</t>
+          <t>40PT 헬스&amp;PT 금릉역점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>decliche32@naver.com</t>
+          <t>40ceo@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1425-4121</t>
+          <t>0507-1355-0702</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 파주시 초롱꽃로 141 B동 7층</t>
+          <t>경기도 파주시 금릉역로 84 2층 204호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://decliche.co.kr/default/</t>
+          <t>https://blog.naver.com/40ceo</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -802,17 +794,13 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5t0nq</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>693</v>
+        <v>28</v>
       </c>
       <c r="Q4" t="n">
-        <v>1186</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1879</v>
+        <v>28</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1628652531</t>
+          <t>1202843378</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1628652531</t>
+          <t>https://m.place.naver.com/place/1202843378</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -853,39 +841,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>디클리셰 24시 스타필드점 헬스 기구필라테스 GX</t>
+          <t>포유짐 헬스PT &amp; 필라테스 운정중앙점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>decliche22@naver.com</t>
+          <t>foru-hongdae@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1415-4121</t>
+          <t>0507-1397-3134</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 파주시 금바위로 42 운정법조타운 3층</t>
+          <t>경기도 파주시 초롱꽃로 133-21 더지음스퀘어 606호, 607호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://decliche.co.kr/default/</t>
+          <t>https://www.instagram.com/foru_unjung/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -895,19 +883,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4fj83</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -919,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>890</v>
+        <v>7</v>
       </c>
       <c r="Q5" t="n">
-        <v>551</v>
+        <v>59</v>
       </c>
       <c r="R5" t="n">
-        <v>1441</v>
+        <v>66</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1320392834</t>
+          <t>2081437541</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1320392834</t>
+          <t>https://m.place.naver.com/place/2081437541</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,34 +940,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>F45 운정</t>
+          <t>온짐 헬스&amp;PT 야당점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>f45unjeong@naver.com</t>
+          <t>on-gym@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1391-6365</t>
+          <t>0507-1437-7707</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 파주시 청암로17번길 21 월드타워5차 701호 702호</t>
+          <t>경기도 파주시 경의로 1068 삼융프라자 4층 403~4호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/f45_unjeong</t>
+          <t>https://pf.kakao.com/_IVxesn/chat</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -998,17 +982,13 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5zxi6</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1017,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>132</v>
+        <v>201</v>
       </c>
       <c r="Q6" t="n">
-        <v>420</v>
+        <v>901</v>
       </c>
       <c r="R6" t="n">
-        <v>552</v>
+        <v>1102</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1564837926</t>
+          <t>1537889737</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1564837926</t>
+          <t>https://m.place.naver.com/place/1537889737</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1054,39 +1034,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>온짐 헬스&amp;PT 야당점</t>
+          <t>S O휘트니스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>on-gym@naver.com</t>
+          <t>starwood0401@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1437-7707</t>
+          <t>031-959-1307</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 파주시 경의로 1068 삼융프라자 4층 403~4호</t>
+          <t>경기도 파주시 법원읍 술이홀로 887 4층 S.O 휘트니스클럽</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_IVxesn/chat</t>
+          <t>https://ok114.co.kr/0319591307</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1096,32 +1076,28 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wphkbsb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>201</v>
+        <v>51</v>
       </c>
       <c r="Q7" t="n">
-        <v>899</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>1100</v>
+        <v>56</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1537889737</t>
+          <t>34516679</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1537889737</t>
+          <t>https://m.place.naver.com/place/34516679</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1152,56 +1128,44 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>머스타드피트니스 운정점</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>mustard_fitness3@naver.com</t>
-        </is>
-      </c>
+          <t>라인업</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1403-6882</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 파주시 와석순환로 86 지앤지프라자 5층</t>
+          <t>경기도 파주시 조리읍 순비골길 7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://www.mustard-fitness.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5itt3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1209,17 +1173,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1042</v>
+        <v>8</v>
       </c>
       <c r="Q8" t="n">
-        <v>124</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>1166</v>
+        <v>9</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1192,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>584588992</t>
+          <t>1188554546</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/584588992</t>
+          <t>https://m.place.naver.com/place/1188554546</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1245,34 +1209,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>다다짐 헬스&amp;PT 운정본점</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dadagym@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1304-1646</t>
+          <t>070-4587-9307</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 파주시 미래로602번길 11 701호,702호</t>
+          <t>경기도 파주시 광탄면 기산리</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dadagym/224242550028</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1282,24 +1246,20 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4v2ogs</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1307,17 +1267,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1286,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1236035000</t>
+          <t>1422172293</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1236035000</t>
+          <t>https://m.place.naver.com/place/1422172293</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1343,34 +1303,30 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>세탁소</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>리바디피티스튜디오</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>rebody7530@naver.com</t>
-        </is>
-      </c>
+          <t>세탁업체헬스장세탁유니폼세탁수건세탁업체,세탁공장</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1331-7549</t>
+          <t>070-8069-4006</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 파주시 경의로 1114 505호</t>
+          <t>경기도 파주시 동패동</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/re_body_pt?igsh=MWFmcWk5OGp6ZWNyMQ==</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1380,7 +1336,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1390,14 +1346,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wjtwmo7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1405,34 +1357,7416 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1432674219</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1432674219</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>대성휘트니스 체형분석운동센터</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>analysisbody@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1421-3170</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>경기도 파주시 한마음1길 40 대성빌딩 5층 대성휘트니스 체형분석운동센터</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/analysisbody</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>14</v>
+      </c>
+      <c r="R11" t="n">
+        <v>23</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>13072835</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13072835</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>광고대행</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>070-4584-2706</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경기도 파주시 동패동</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1088229104</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1088229104</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>인터넷상거래</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>070-8934-5353</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>경기도 파주시 오도동</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1218501609</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1218501609</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>인터넷상거래</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>070-8934-3868</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>경기도 파주시 금릉동</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1466756114</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1466756114</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>파이 피트니스 스타필드점 헬스PT스피닝</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>pifitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1350-3458</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>경기도 파주시 경의로1240번길 14-11 8층</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/pifitness?tab=1&amp;trackingCode=blog_feed_mobile</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>481</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2323</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2804</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1448948729</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1448948729</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>조아짐</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>joagympaju@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1428-9720</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>경기도 파주시 번뛰기길 69-10 1층</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/joagympaju</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>61</v>
+      </c>
+      <c r="R16" t="n">
+        <v>69</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1037638892</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1037638892</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>마이스쿼시 &amp; 헬스</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>mysquashealth@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1458-0074</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>경기도 파주시 중앙로 308 현대 금촌타워상가 6층 605호 606호 607호</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mysquashealth</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>171</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>165</v>
+      </c>
+      <c r="R17" t="n">
+        <v>336</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1238118590</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1238118590</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>인터넷상거래</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>070-8934-0606</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>경기도 파주시 광탄면 기산리</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1104684204</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1104684204</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>짐원휘트니스 여성전용 해오름3호점 헬스PT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>gymone3@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>경기도 파주시 해올2길 21 월드타워 19차 4층</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gymone3</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>246</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>176</v>
+      </c>
+      <c r="R19" t="n">
+        <v>422</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1542602413</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1542602413</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>광고대행</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>070-4595-2612</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>경기도 파주시 아동동</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1096077727</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1096077727</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>토브짐</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gjtpdud777@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1370-0723</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>경기도 파주시 조리읍 통일로 324 덕도빌딩 3층, 4층 토브짐</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>http://instagram.com/tovgymfitness</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>221</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>85</v>
+      </c>
+      <c r="R21" t="n">
+        <v>306</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1400651912</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1400651912</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>더 블랙 피트니스</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>theblack_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1341-6432</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>경기도 파주시 청석로 260 트리플메디칼타워 4층 더 블랙 피트니스</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://litt.ly/theblack_fitness</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>28</v>
+      </c>
+      <c r="R22" t="n">
+        <v>80</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1340211997</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1340211997</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>607짐</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>607gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1498-1572</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>경기도 파주시 청석로 262 607호</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/607gym</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2</v>
+      </c>
+      <c r="R23" t="n">
+        <v>13</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1717011354</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1717011354</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>F45 운정</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>f45unjeong@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1391-6365</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>경기도 파주시 청암로17번길 21 월드타워5차 701호 702호</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/f45_unjeong</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>132</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>420</v>
+      </c>
+      <c r="R24" t="n">
+        <v>552</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1564837926</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1564837926</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>플랜에이짐</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>plan_a_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>경기도 파주시 조리읍 통일로 317 401,402호</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>http://플랜에이짐.kr</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>127</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>165</v>
+      </c>
+      <c r="R25" t="n">
+        <v>292</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1939906854</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1939906854</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>노이짐휘트니스</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>noigym12@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>031-957-9679</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>경기도 파주시 청암로17번길 43 운정베스트프라자 7층</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/noigym12</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>130</v>
+      </c>
+      <c r="R26" t="n">
+        <v>184</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1868011250</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1868011250</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>88휘트니스 헬스&amp;PT&amp;GX</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>88fitness-@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1402-7494</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>경기도 파주시 숲속노을로 275 6층 601호~603호</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_mAvxoxj</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>302</v>
+      </c>
+      <c r="R27" t="n">
+        <v>433</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1515129267</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1515129267</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>광고대행</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>070-4573-5526</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>경기도 파주시 군내면 읍내리</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1494286135</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1494286135</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>아르젠 휘트니스 금촌점 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>arzenfitness_2@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>경기도 파주시 번영로 20 402-1호,403호,404호,405호</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/arzen_fitness2</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>223</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>245</v>
+      </c>
+      <c r="R29" t="n">
+        <v>468</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1698425557</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1698425557</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>미라클짐 운정점 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>miraclegym1@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1498-0268</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>경기도 파주시 미래로 377 운정스퀘어 7F</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/miraclegym1</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>1641</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>307</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1948</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1153230644</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1153230644</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>머스타드피트니스 운정점</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>mustard_fitness3@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1403-6882</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>경기도 파주시 와석순환로 86 지앤지프라자 5층</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>http://www.mustard-fitness.com</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>1042</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>124</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1166</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>584588992</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/584588992</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>플렉스짐 야당</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>flexgymyadang@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1416-3798</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>경기도 파주시 경의로 1100 연세프라자 3층</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/flexgymyadang</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>396</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>712</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1108</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1688298200</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1688298200</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>힙디자인팩토리 헬스PT 산내다율점</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>natural_sehun@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1411-1783</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>경기도 파주시 해올1길 7 4층 힙디자인팩토리 운정산내</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/natural_sehun/223137384574</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>77</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1285495775</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1285495775</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>체육관</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>헬스케어센터</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>powerlifter@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>050-6514-8789</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>경기도 파주시 청암로17번길 29 스타빌딩 10층</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/powerlifter</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2</v>
+      </c>
+      <c r="R34" t="n">
+        <v>4</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>278193572</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/278193572</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>광고대행</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>070-4595-7072</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>경기도 파주시 파주읍 백석리</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1295009794</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1295009794</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>스카이짐</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>sky-gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1342-9714</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>경기도 파주시 경의로 1066 6층 603호</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/SKYGYM_YADANG</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>27</v>
+      </c>
+      <c r="R36" t="n">
+        <v>37</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1429060510</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1429060510</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>카달로그인쇄</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>070-4595-7091</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>경기도 파주시 오도동</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1505026754</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1505026754</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>인터넷상거래</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>070-8934-4105</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>경기도 파주시 문발동</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1932095896</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1932095896</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>스타헬스</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>147048@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>경기도 파주시 파주읍 술이홀로 463</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2</v>
+      </c>
+      <c r="R39" t="n">
+        <v>5</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1683936538</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1683936538</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>포워드휘트니스 헬스&amp;PT 금릉점</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>forward-fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1426-6693</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>경기도 파주시 금릉역로 84 9층 905, 906, 907호</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://pcmap.place.naver.com/place/1809060918/ticket</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>491</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>522</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1013</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1809060918</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1809060918</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>카달로그인쇄</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>070-4592-8380</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>경기도 파주시 목동동</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1090259104</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1090259104</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>본피트니스 운정점</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>bornfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1472-5081</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>경기도 파주시 청암로17번길 45 401호</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bornfitness</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>101</v>
+      </c>
+      <c r="R42" t="n">
+        <v>186</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>2002476589</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2002476589</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>인터넷상거래</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>070-8934-2696</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>경기도 파주시 연다산동</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1021398037</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1021398037</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>오도리체육관</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>odorigym@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1408-7915</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>경기도 파주시 오도로 26-41 오도리체육관(카카오네비X길없음)</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/odorigym/</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>136</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>99</v>
+      </c>
+      <c r="R44" t="n">
+        <v>235</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1132132429</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1132132429</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>제이제이짐</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1321-2759</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>경기도 파주시 탄현면 엘씨디로241번길 35 휴림빌딩 3층 301호, 302호</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>4</v>
+      </c>
+      <c r="R45" t="n">
+        <v>11</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1544645620</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1544645620</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>인터넷상거래</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>070-8934-3694</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>경기도 파주시 교하동</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1054585792</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1054585792</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>헬스클럽</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2601120@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>031-943-8245</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>경기도 파주시 심학산로423번길 7-25</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" t="n">
+        <v>2</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1509200791</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1509200791</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>더엠 휘트니스</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>fittown02@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>031-944-8883</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>경기도 파주시 와석순환로 135 신한프라자 4층/5층</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_SjVxfxj</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>159</v>
+      </c>
+      <c r="R48" t="n">
+        <v>260</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>760573466</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/760573466</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>매직인터내셔날</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>auroraint@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>031-949-7964</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>경기도 파주시 탄현면 한산로 5-29 엠지스포츠</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>http://www.mg-sports.co.kr/</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>2</v>
+      </c>
+      <c r="R49" t="n">
+        <v>2</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>35553752</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35553752</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>엔비어스짐 PT &amp; 엔비필라테스</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>schooi123@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1470-7581</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>경기도 파주시 중앙로 328 MH타워 10층 1001~1004호</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/envyusgym</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>1905</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>313</v>
+      </c>
+      <c r="R50" t="n">
+        <v>2218</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>37008765</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37008765</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>인터넷상거래</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>070-8934-2463</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>경기도 파주시 송촌동</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1925909033</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1925909033</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>연리지 휘트니스 헬스&amp;골프</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>csys026@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>070-8150-7795</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>경기도 파주시 해솔로 20</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>6</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1031908971</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1031908971</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>인터넷상거래</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>070-8934-8918</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>경기도 파주시 군내면 읍내리</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1113833307</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1113833307</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>피트인365 파주문산점</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>fitin7@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>031-953-6889</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>경기도 파주시 문산읍 방촌로 1759 홈플러스파주문산점 2층</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fitin365_paju_</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>22</v>
+      </c>
+      <c r="R54" t="n">
+        <v>108</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1818987768</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1818987768</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>키스짐 금촌점</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>kieees_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1438-9970</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>경기도 파주시 한마음1길 38 골드시티프라자 5층 키스짐</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/kieees_gym</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>504</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>369</v>
+      </c>
+      <c r="R55" t="n">
+        <v>873</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1587590429</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1587590429</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>펀치레이디</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>tigerj0725@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1494-8309</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>경기도 파주시 청석로 262 3층</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/tigerj0725</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>213</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1144</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1357</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>34605120</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/34605120</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>FM피트니스 금촌점</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>dopaming-@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1333-8294</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>경기도 파주시 시청로 3-9 1층</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>9</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>2027037482</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2027037482</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>라인짐 문산점</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>linegym_munsan@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>경기도 파주시 문산읍 문향로49번길 20 로얄 빌딩 10층 라인짐</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/linegym_munsan</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>117</v>
+      </c>
+      <c r="R58" t="n">
+        <v>203</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>21207445</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21207445</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>오빠짐</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>oppagym@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1306-4271</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>경기도 파주시 교하로159번길 7 목동트윈프라자 2차 504호</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>2</v>
+      </c>
+      <c r="R59" t="n">
+        <v>10</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1007064699</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1007064699</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>아르젠 휘트니스</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>arzenfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1371-3419</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>경기도 파주시 초롱꽃로 117-10 아르젠 라스퀘어2차 7층</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/arzen_fitness</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>217</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>489</v>
+      </c>
+      <c r="R60" t="n">
+        <v>706</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1934265979</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1934265979</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>프라임VIP피트니스/헬스PT</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>taross@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1322-9633</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>경기도 파주시 한울로 59 5층</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://cafe.naver.com/muscleprime</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>317</v>
+      </c>
+      <c r="R61" t="n">
+        <v>391</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1189590226</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1189590226</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>인터넷상거래</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>070-8934-1838</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>경기도 파주시 아동동</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1508213265</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1508213265</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>디클리셰 24시 다율점 헬스 기구필라테스 PT</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>decliche12@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1371-4121</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>경기도 파주시 해올1길 31 이타워2 7층</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://decliche.co.kr/default/</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>1565</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>996</v>
+      </c>
+      <c r="R63" t="n">
+        <v>2561</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1538587440</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1538587440</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>디클리셰 24시 GTX점 헬스 기구필라테스 스피닝 GX</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>decliche32@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1425-4121</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>경기도 파주시 초롱꽃로 141 B동 7층</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://decliche.co.kr/default/</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>693</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1201</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1894</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1628652531</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1628652531</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>로망휘트니스 헬스 PT 태닝</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>kik4985@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1314-9178</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>경기도 파주시 책향기로 419 8층</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_Fxamxmxj</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>476</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>684</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1160</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1337216446</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1337216446</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>나애다짐</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>jitaejo@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1302-1923</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>경기도 파주시 와석순환로 70 신운정프라자2 5층 나애다짐</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_rhsas</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>119</v>
+      </c>
+      <c r="R66" t="n">
+        <v>134</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>31389209</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31389209</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>30여성순환운동뷰티클30플러스</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>sikrrot@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>031-957-7369</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>경기도 파주시 금빛로 27 광장프라자 504호</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>http://cafe.naver.com/pajubeauticle30/</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>3</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>13355519</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13355519</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>올마이티짐 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>almg-yadang@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1460-1270</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>경기도 파주시 경의로 1042 7층 올마이티짐</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_xbxlxnGn</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>715</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>283</v>
+      </c>
+      <c r="R68" t="n">
+        <v>998</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1141836591</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1141836591</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>마이헬스 &amp; PT</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>myhealth72@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1304-0301</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>경기도 파주시 중앙로 308 금촌 현대타워 6층 605호 606호 607호</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/myhealth72</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>44</v>
+      </c>
+      <c r="R69" t="n">
+        <v>124</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1862528462</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1862528462</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>광고대행</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>070-4587-7703</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>경기도 파주시 송촌동</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1321636294</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1321636294</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>인터넷상거래</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>070-8934-3415</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>경기도 파주시 목동동</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>1</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1320502098</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1320502098</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>디클리셰 가람마을점 헬스&amp;필라테스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>decliche44@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>경기도 파주시 가람로 124 401~405호</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/decliche_4/</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>232</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>487</v>
+      </c>
+      <c r="R72" t="n">
+        <v>719</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1773137610</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1773137610</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>카달로그인쇄</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>070-4595-7060</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>경기도 파주시 탄현면 갈현리</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1354958219</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1354958219</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>광고대행</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>070-4573-9226</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>경기도 파주시 하지석동</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1162704294</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1162704294</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>상업세탁물</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>플렉스엠앤오</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>whitecap0424@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1394-3984</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>경기도 파주시 조리읍 매봉재길 99-10</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://www.flexmno.com</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>2079626557</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2079626557</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>스포츠센터</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>코오롱스포렉스 주내점</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ohnie@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1364-2553</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>경기도 파주시 파주읍 술이홀로 305 파주문화체육센터 코오롱스포렉스 주내점</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>http://paju5.sporex.com/</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>455</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>26</v>
+      </c>
+      <c r="R76" t="n">
+        <v>481</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1354657006</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1354657006</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>로드짐 야당점</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>roadgym86@naver.com</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0507-1458-6779</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>경기도 파주시 경의로1004번길 33 3층 303호</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/road_gym_</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>116</v>
+      </c>
+      <c r="R77" t="n">
+        <v>197</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>1959563259</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1959563259</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>교하청석스포츠센터</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>nolovecj@naver.com</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>031-943-5596</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>경기도 파주시 청석로 370 교하청석스포츠센터</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://paju2.sporex.com</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>566</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>55</v>
+      </c>
+      <c r="R78" t="n">
+        <v>621</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>21398823</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21398823</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>숨PT</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>vivianpila@naver.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>경기도 파주시 금빛로 22 603호</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/vivianpila</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>2097611097</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2097611097</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>베이스짐</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>basegyms@naver.com</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>경기도 파주시 심학산로423번길 7-37 애플프라자 501호 베이스짐</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/basegyms</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>80</v>
+      </c>
+      <c r="R80" t="n">
+        <v>139</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>1003798882</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1003798882</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>경기미래교육 파주캠퍼스 스포츠센터</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>gill_forum@naver.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>031-956-2222</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>경기도 파주시 탄현면 얼음실로 40</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://gill.or.kr/gill/cntnts/i-121/web.do</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>12</v>
+      </c>
+      <c r="R81" t="n">
+        <v>22</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>13162756</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13162756</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>코오롱스포렉스 동패점</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ahrhddl@naver.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>031-948-8033</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>경기도 파주시 와석순환로172번길 30 코오롱스포렉스 동패점</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>http://paju6.sporex.com</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>666</v>
+      </c>
+      <c r="Q82" t="n">
         <v>35</v>
       </c>
-      <c r="Q10" t="n">
-        <v>28</v>
-      </c>
-      <c r="R10" t="n">
-        <v>63</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2037075259</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2037075259</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
+      <c r="R82" t="n">
+        <v>701</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>1898693324</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1898693324</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>베스트피지컬짐 문산점</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>cloder132@naver.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0507-1464-8797</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>경기도 파주시 문산읍 문향로 72-1 문산타워 8층</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/cloder132</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>137</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>70</v>
+      </c>
+      <c r="R83" t="n">
+        <v>207</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>1065456469</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1065456469</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>강종근트레이닝센터 광탄점</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>healthjk@naver.com</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0507-1436-0130</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>경기도 파주시 광탄면 큰여울길 35 동해프라자 2층</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/healthjk</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>2</v>
+      </c>
+      <c r="R84" t="n">
+        <v>2</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>1696200831</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1696200831</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>라이프짐 PT STUDIO</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>lastlifept@naver.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>031-948-9694</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>경기도 파주시 경의로 1090 삼융타워 6F 603호 라이프짐</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_SxoYxaj</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>17</v>
+      </c>
+      <c r="R85" t="n">
+        <v>17</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>1188939336</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1188939336</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>피지컬PT스튜디오</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>skdldlsdn@naver.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>0507-1350-5343</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>경기도 파주시 청암로17번길 25 운정블루 6층</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>http://instagram.com/physical_pt</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>130</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" t="n">
+        <v>130</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>1124279003</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1124279003</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>운동상점</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>undongsangjum@naver.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0507-1419-0806</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>경기도 파주시 경의로1004번길 17 2층 10호</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/exercise_store</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>2074196749</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2074196749</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>올인피티샵 운정점</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>dbgmltn9118@naver.com</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0507-1336-9024</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>경기도 파주시 경의로 1218 3층 312호</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dbgmltn9118</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>93</v>
+      </c>
+      <c r="R88" t="n">
+        <v>180</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>1937555695</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1937555695</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>제이엘 필라테스&amp;그래비티 금촌점</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>jlpaju2019@naver.com</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0507-1367-0383</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>경기도 파주시 후곡로 1 303호</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jlpaju2019/224126426195</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>264</v>
+      </c>
+      <c r="R89" t="n">
+        <v>295</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>1478246403</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1478246403</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/파주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/파주_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="39" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -564,24 +564,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>파이 피트니스 스타필드점 헬스PT스피닝</t>
+          <t>파이 피트니스 다율점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>pifitness@naver.com</t>
+          <t>pifitness02@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1350-3458</t>
+          <t>0507-1436-5392</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 파주시 경의로1240번길 14-11 8층</t>
+          <t>경기 파주시 해올2길 8 1006~1009호(다율동)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wl490ee</t>
+          <t>https://talk.naver.com/ct/whg35h5</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>483</v>
+        <v>31</v>
       </c>
       <c r="Q2" t="n">
-        <v>2323</v>
+        <v>72</v>
       </c>
       <c r="R2" t="n">
-        <v>2806</v>
+        <v>103</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1448948729</t>
+          <t>2076933270</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1448948729</t>
+          <t>https://m.place.naver.com/place/2076933270</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -662,55 +662,59 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>디클리셰 24시 GTX점 헬스 기구필라테스 스피닝 GX</t>
+          <t>파이 피트니스 스타필드점 헬스PT스피닝</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>decliche32@naver.com</t>
+          <t>pifitness@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1425-4121</t>
+          <t>0507-1350-3458</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 파주시 초롱꽃로 141 B동 7층</t>
+          <t>경기 파주시 경의로1240번길 14-11 8층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://decliche.co.kr/default/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wl490ee</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>693</v>
+        <v>483</v>
       </c>
       <c r="Q3" t="n">
-        <v>1202</v>
+        <v>2324</v>
       </c>
       <c r="R3" t="n">
-        <v>1895</v>
+        <v>2807</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1628652531</t>
+          <t>1448948729</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1628652531</t>
+          <t>https://m.place.naver.com/place/1448948729</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -756,24 +760,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>디클리셰 24시 스타필드점 헬스 기구필라테스 GX</t>
+          <t>디클리셰 24시 GTX점 헬스 기구필라테스 스피닝 GX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>decliche12@naver.com</t>
+          <t>decliche32@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1415-4121</t>
+          <t>0507-1425-4121</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 파주시 금바위로 42 운정법조타운 3층</t>
+          <t>경기도 파주시 초롱꽃로 141 B동 7층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -803,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4fj83</t>
+          <t>https://talk.naver.com/ct/w5t0nq</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -817,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>890</v>
+        <v>693</v>
       </c>
       <c r="Q4" t="n">
-        <v>554</v>
+        <v>1208</v>
       </c>
       <c r="R4" t="n">
-        <v>1444</v>
+        <v>1901</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1320392834</t>
+          <t>1628652531</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1320392834</t>
+          <t>https://m.place.naver.com/place/1628652531</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -854,44 +858,44 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>F45 운정</t>
+          <t>디클리셰 24시 스타필드점 헬스 기구필라테스 GX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>f45unjeong@naver.com</t>
+          <t>decliche12@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1391-6365</t>
+          <t>0507-1415-4121</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 파주시 청암로17번길 21 월드타워5차 701호 702호</t>
+          <t>경기 파주시 금바위로 42 운정법조타운 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://decliche.co.kr/default/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -901,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5zxi6</t>
+          <t>https://talk.naver.com/ct/w4fj83</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -915,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>132</v>
+        <v>890</v>
       </c>
       <c r="Q5" t="n">
-        <v>420</v>
+        <v>556</v>
       </c>
       <c r="R5" t="n">
-        <v>552</v>
+        <v>1446</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1564837926</t>
+          <t>1320392834</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1564837926</t>
+          <t>https://m.place.naver.com/place/1320392834</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -952,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>온짐 헬스&amp;PT 야당점</t>
+          <t>F45 운정</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>on-gym@naver.com</t>
+          <t>f45unjeong@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1437-7707</t>
+          <t>0507-1391-6365</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로 1068 삼융프라자 4층 403~4호</t>
+          <t>경기 파주시 청암로17번길 21 월드타워5차 701호 702호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/f45_unjeong</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -984,7 +988,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -999,12 +1003,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wphkbsb</t>
+          <t>https://talk.naver.com/ct/w5zxi6</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1013,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>201</v>
+        <v>132</v>
       </c>
       <c r="Q6" t="n">
-        <v>904</v>
+        <v>420</v>
       </c>
       <c r="R6" t="n">
-        <v>1105</v>
+        <v>552</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,17 +1032,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1537889737</t>
+          <t>1564837926</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1537889737</t>
+          <t>https://m.place.naver.com/place/1564837926</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1050,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>머스타드피트니스 운정점</t>
+          <t>온짐 헬스&amp;PT 야당점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mustard_fitness3@naver.com</t>
+          <t>on-gym@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1403-6882</t>
+          <t>0507-1437-7707</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 파주시 와석순환로 86 지앤지프라자 5층</t>
+          <t>경기도 파주시 경의로 1068 삼융프라자 4층 403~4호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://www.mustard-fitness.com</t>
+          <t>https://pf.kakao.com/_IVxesn/chat</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,22 +1091,18 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5itt3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1042</v>
+        <v>201</v>
       </c>
       <c r="Q7" t="n">
-        <v>124</v>
+        <v>907</v>
       </c>
       <c r="R7" t="n">
-        <v>1166</v>
+        <v>1108</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>584588992</t>
+          <t>1537889737</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/584588992</t>
+          <t>https://m.place.naver.com/place/1537889737</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1148,34 +1148,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>에스엠짐 파주본점</t>
+          <t>머스타드피트니스 운정점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>spyangel2@naver.com</t>
+          <t>mustard_fitness3@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1370-4147</t>
+          <t>0507-1403-6882</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 파주시 교하로 957 1, 2층 에스엠짐</t>
+          <t>경기도 파주시 와석순환로 86 지앤지프라자 5층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spyangel2</t>
+          <t>http://www.mustard-fitness.com</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1190,10 +1190,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5itt3</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1205,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>114</v>
+        <v>1042</v>
       </c>
       <c r="Q8" t="n">
-        <v>1428</v>
+        <v>124</v>
       </c>
       <c r="R8" t="n">
-        <v>1542</v>
+        <v>1166</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,46 +1224,46 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1184875775</t>
+          <t>584588992</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1184875775</t>
+          <t>https://m.place.naver.com/place/584588992</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>애블바디PT 초롱꽃마을 2호점 헬스PT</t>
+          <t>다다짐 헬스&amp;PT 운정본점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>every_body_pt@naver.com</t>
+          <t>dadagym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1427-5294</t>
+          <t>0507-1304-1646</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 파주시 양지로 117 304호,305호</t>
+          <t>경기 파주시 미래로602번길 11 701호,702호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1289,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wdljl0j</t>
+          <t>https://talk.naver.com/ct/w4v2ogs</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1299,17 +1303,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="Q9" t="n">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="R9" t="n">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,46 +1322,46 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2038397745</t>
+          <t>1236035000</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2038397745</t>
+          <t>https://m.place.naver.com/place/1236035000</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>애블바디PT 해오름마을 1호점 헬스PT</t>
+          <t>에스엠짐 파주본점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>every_body_pt@naver.com</t>
+          <t>spyangel2@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1362-5290</t>
+          <t>0507-1370-4147</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 파주시 해올2길 16 공감빌딩 6층 애블바디 P.T샵</t>
+          <t>경기 파주시 교하로 957 1, 2층 에스엠짐</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1382,14 +1386,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w44dez</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>148</v>
+        <v>114</v>
       </c>
       <c r="Q10" t="n">
-        <v>276</v>
+        <v>1428</v>
       </c>
       <c r="R10" t="n">
-        <v>424</v>
+        <v>1542</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,17 +1416,115 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1831911897</t>
+          <t>1184875775</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1831911897</t>
+          <t>https://m.place.naver.com/place/1184875775</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>리바디피티스튜디오</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>rebody7530@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1331-7549</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>경기도 파주시 경의로 1114 505호</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wjtwmo7</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>28</v>
+      </c>
+      <c r="R11" t="n">
+        <v>63</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2037075259</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2037075259</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/파주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/파주_헬스장.xlsx
@@ -422,11 +422,11 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>디클리셰 24시 GTX점 헬스 기구필라테스 스피닝 GX</t>
+          <t>파이 피트니스 다율점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>decliche32@naver.com</t>
+          <t>pifitness02@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1425-4121</t>
+          <t>0507-1436-5392</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 파주시 초롱꽃로 141 B동 7층</t>
+          <t>경기 파주시 해올2길 8 1006~1009호(다율동)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://decliche.co.kr/default/</t>
+          <t>https://open.kakao.com/o/sWflSZei</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5t0nq</t>
+          <t>https://talk.naver.com/ct/whg35h5</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>694</v>
+        <v>36</v>
       </c>
       <c r="Q2" t="n">
-        <v>1253</v>
+        <v>72</v>
       </c>
       <c r="R2" t="n">
-        <v>1947</v>
+        <v>108</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1628652531</t>
+          <t>2076933270</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1628652531</t>
+          <t>https://m.place.naver.com/place/2076933270</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,44 +662,44 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>파이 피트니스 스타필드점 헬스PT스피닝</t>
+          <t>디클리셰 24시 GTX점 헬스 기구필라테스 스피닝 GX</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pifitness@naver.com</t>
+          <t>decliche32@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1350-3458</t>
+          <t>0507-1425-4121</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 파주시 경의로1240번길 14-11 8층</t>
+          <t>경기 파주시 초롱꽃로 141 B동 7층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://decliche.co.kr/default/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wl490ee</t>
+          <t>https://talk.naver.com/ct/w5t0nq</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>483</v>
+        <v>696</v>
       </c>
       <c r="Q3" t="n">
-        <v>2325</v>
+        <v>1283</v>
       </c>
       <c r="R3" t="n">
-        <v>2808</v>
+        <v>1979</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1448948729</t>
+          <t>1628652531</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1448948729</t>
+          <t>https://m.place.naver.com/place/1628652531</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,34 +760,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>디클리셰 24시 스타필드점 헬스 기구필라테스 GX</t>
+          <t>파이 피트니스 스타필드점 헬스PT스피닝</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>decliche12@naver.com</t>
+          <t>pifitness@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1415-4121</t>
+          <t>0507-1350-3458</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 파주시 금바위로 42 운정법조타운 3층</t>
+          <t>경기 파주시 경의로1240번길 14-11 8층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://decliche.co.kr/default/</t>
+          <t>https://blog.naver.com/pifitness?tab=1&amp;trackingCode=blog_feed_mobile</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4fj83</t>
+          <t>https://talk.naver.com/ct/wl490ee</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>893</v>
+        <v>483</v>
       </c>
       <c r="Q4" t="n">
-        <v>564</v>
+        <v>2298</v>
       </c>
       <c r="R4" t="n">
-        <v>1457</v>
+        <v>2781</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1320392834</t>
+          <t>1448948729</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1320392834</t>
+          <t>https://m.place.naver.com/place/1448948729</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,44 +858,44 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>F45 운정</t>
+          <t>디클리셰 24시 스타필드점 헬스 기구필라테스 GX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>f45unjeong@naver.com</t>
+          <t>decliche22@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1391-6365</t>
+          <t>0507-1415-4121</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 파주시 청암로17번길 21 월드타워5차 701호 702호</t>
+          <t>경기 파주시 금바위로 42 운정법조타운 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://decliche.co.kr/default/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5zxi6</t>
+          <t>https://talk.naver.com/ct/w4fj83</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>132</v>
+        <v>894</v>
       </c>
       <c r="Q5" t="n">
-        <v>420</v>
+        <v>570</v>
       </c>
       <c r="R5" t="n">
-        <v>552</v>
+        <v>1464</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1564837926</t>
+          <t>1320392834</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1564837926</t>
+          <t>https://m.place.naver.com/place/1320392834</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>온짐 헬스&amp;PT 야당점</t>
+          <t>F45 운정</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>on-gym@naver.com</t>
+          <t>f45unjeong@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1437-7707</t>
+          <t>0507-1391-6365</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로 1068 삼융프라자 4층 403~4호</t>
+          <t>경기 파주시 청암로17번길 21 월드타워5차 701호 702호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/f45_unjeong</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wphkbsb</t>
+          <t>https://talk.naver.com/ct/w5zxi6</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>202</v>
+        <v>132</v>
       </c>
       <c r="Q6" t="n">
-        <v>914</v>
+        <v>421</v>
       </c>
       <c r="R6" t="n">
-        <v>1116</v>
+        <v>553</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1537889737</t>
+          <t>1564837926</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1537889737</t>
+          <t>https://m.place.naver.com/place/1564837926</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1054,39 +1054,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>에스엠짐 파주본점</t>
+          <t>온짐 헬스&amp;PT 야당점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>spyangel2@naver.com</t>
+          <t>on-gym@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1370-4147</t>
+          <t>0507-1437-7707</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 파주시 교하로 957 1, 2층 에스엠짐</t>
+          <t>경기 파주시 경의로 1068 삼융프라자 4층 403~4호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_IVxesn/chat</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1096,13 +1096,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wphkbsb</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1111,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>114</v>
+        <v>202</v>
       </c>
       <c r="Q7" t="n">
-        <v>1429</v>
+        <v>923</v>
       </c>
       <c r="R7" t="n">
-        <v>1543</v>
+        <v>1125</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1184875775</t>
+          <t>1537889737</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1184875775</t>
+          <t>https://m.place.naver.com/place/1537889737</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1143,39 +1147,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>애블바디PT 해오름마을 1호점 헬스PT</t>
+          <t>1퍼센트짐 금릉점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>every_body_pt@naver.com</t>
+          <t>1percentgym2@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1362-5290</t>
+          <t>0507-1386-4598</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 파주시 해올2길 16 공감빌딩 6층 애블바디 P.T샵</t>
+          <t>경기 파주시 금빛로 4-1 3층 301호,302호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://booking.naver.com/booking/6/bizes/1113882</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1195,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w44dez</t>
+          <t>https://talk.naver.com/ct/w5yr9z</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1205,17 +1209,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>148</v>
+        <v>387</v>
       </c>
       <c r="Q8" t="n">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="R8" t="n">
-        <v>425</v>
+        <v>654</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1831911897</t>
+          <t>1714420485</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1831911897</t>
+          <t>https://m.place.naver.com/place/1714420485</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1246,34 +1250,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>더 블랙 피트니스</t>
+          <t>에스엠짐 파주본점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>theblack_fitness@naver.com</t>
+          <t>spyangel2@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1341-6432</t>
+          <t>0507-1370-4147</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 파주시 청석로 260 트리플메디칼타워 4층 더 블랙 피트니스</t>
+          <t>경기 파주시 교하로 957 1, 2층 에스엠짐</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://litt.ly/theblack_fitness</t>
+          <t>https://blog.naver.com/spyangel2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1283,19 +1287,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wvjoz2r</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>52</v>
+        <v>114</v>
       </c>
       <c r="Q9" t="n">
-        <v>28</v>
+        <v>1430</v>
       </c>
       <c r="R9" t="n">
-        <v>80</v>
+        <v>1544</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1340211997</t>
+          <t>1184875775</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1340211997</t>
+          <t>https://m.place.naver.com/place/1184875775</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1344,39 +1344,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>나나짐PT1대1전문헬스장 파주운정점</t>
+          <t>애블바디PT 초롱꽃마을 2호점 헬스PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nanagym@naver.com</t>
+          <t>every_body_pt@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1304-9673</t>
+          <t>0507-1427-5294</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 파주시 교하로159번길 45 힐링플러스 4층 402호</t>
+          <t>경기 파주시 양지로 117 304호,305호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://smartstore.naver.com/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ueng</t>
+          <t>https://talk.naver.com/ct/wdljl0j</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="Q10" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="R10" t="n">
-        <v>108</v>
+        <v>36</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1327274793</t>
+          <t>2038397745</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1327274793</t>
+          <t>https://m.place.naver.com/place/2038397745</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1442,34 +1442,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>리바디피티스튜디오</t>
+          <t>애블바디PT 해오름마을 1호점 헬스PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>rebody7530@naver.com</t>
+          <t>every_body_pt@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1331-7549</t>
+          <t>0507-1362-5290</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로 1114 505호</t>
+          <t>경기 파주시 해올2길 16 공감빌딩 6층 애블바디 P.T샵</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/re_body_pt?igsh=MWFmcWk5OGp6ZWNyMQ==</t>
+          <t>https://smartstore.naver.com/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1484,10 +1484,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w44dez</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1495,17 +1499,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>35</v>
+        <v>148</v>
       </c>
       <c r="Q11" t="n">
-        <v>28</v>
+        <v>277</v>
       </c>
       <c r="R11" t="n">
-        <v>63</v>
+        <v>425</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,12 +1518,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2037075259</t>
+          <t>1831911897</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2037075259</t>
+          <t>https://m.place.naver.com/place/1831911897</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/파주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/파주_헬스장.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -591,7 +591,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -628,10 +628,10 @@
         <v>36</v>
       </c>
       <c r="Q2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -662,34 +662,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>디클리셰 24시 GTX점 헬스 기구필라테스 스피닝 GX</t>
+          <t>파이 피트니스 스타필드점 헬스PT스피닝</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>decliche32@naver.com</t>
+          <t>pifitness@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1425-4121</t>
+          <t>0507-1350-3458</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 파주시 초롱꽃로 141 B동 7층</t>
+          <t>경기 파주시 경의로1240번길 14-11 8층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://decliche.co.kr/default/</t>
+          <t>https://blog.naver.com/pifitness?tab=1&amp;trackingCode=blog_feed_mobile</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5t0nq</t>
+          <t>https://talk.naver.com/ct/wl490ee</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>696</v>
+        <v>483</v>
       </c>
       <c r="Q3" t="n">
-        <v>1283</v>
+        <v>2298</v>
       </c>
       <c r="R3" t="n">
-        <v>1979</v>
+        <v>2781</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1628652531</t>
+          <t>1448948729</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1628652531</t>
+          <t>https://m.place.naver.com/place/1448948729</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -760,34 +760,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>파이 피트니스 스타필드점 헬스PT스피닝</t>
+          <t>디클리셰 24시 GTX점 헬스 기구필라테스 스피닝 GX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pifitness@naver.com</t>
+          <t>decliche32@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1350-3458</t>
+          <t>0507-1425-4121</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 파주시 경의로1240번길 14-11 8층</t>
+          <t>경기도 파주시 초롱꽃로 141 B동 7층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pifitness?tab=1&amp;trackingCode=blog_feed_mobile</t>
+          <t>https://decliche.co.kr/default/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -802,17 +802,13 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wl490ee</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>483</v>
+        <v>697</v>
       </c>
       <c r="Q4" t="n">
-        <v>2298</v>
+        <v>1284</v>
       </c>
       <c r="R4" t="n">
-        <v>2781</v>
+        <v>1981</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +832,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1448948729</t>
+          <t>1628652531</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1448948729</t>
+          <t>https://m.place.naver.com/place/1628652531</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -944,7 +940,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1038,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1067,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 파주시 경의로 1068 삼융프라자 4층 403~4호</t>
+          <t>경기도 파주시 경의로 1068 삼융프라자 4층 403~4호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1096,14 +1092,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wphkbsb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>O</t>
@@ -1140,7 +1132,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1152,29 +1144,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1퍼센트짐 금릉점 헬스&amp;PT</t>
+          <t>머스타드피트니스 운정점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1percentgym2@naver.com</t>
+          <t>mustard_fitness3@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1386-4598</t>
+          <t>0507-1403-6882</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 파주시 금빛로 4-1 3층 301호,302호</t>
+          <t>경기도 파주시 와석순환로 86 지앤지프라자 5층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/1113882</t>
+          <t>http://www.mustard-fitness.com</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1184,24 +1176,20 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5yr9z</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1213,13 +1201,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>387</v>
+        <v>1045</v>
       </c>
       <c r="Q8" t="n">
-        <v>267</v>
+        <v>124</v>
       </c>
       <c r="R8" t="n">
-        <v>654</v>
+        <v>1169</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1216,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1714420485</t>
+          <t>584588992</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1714420485</t>
+          <t>https://m.place.naver.com/place/584588992</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1238,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>에스엠짐 파주본점</t>
+          <t>다다짐 헬스&amp;PT 운정본점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>spyangel2@naver.com</t>
+          <t>dadagym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1370-4147</t>
+          <t>0507-1304-1646</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 파주시 교하로 957 1, 2층 에스엠짐</t>
+          <t>경기 파주시 미래로602번길 11 701호,702호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spyangel2</t>
+          <t>https://blog.naver.com/dadagym/224242550028</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1292,10 +1280,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4v2ogs</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1307,13 +1299,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>114</v>
+        <v>59</v>
       </c>
       <c r="Q9" t="n">
-        <v>1430</v>
+        <v>70</v>
       </c>
       <c r="R9" t="n">
-        <v>1544</v>
+        <v>129</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,51 +1314,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1184875775</t>
+          <t>1236035000</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1184875775</t>
+          <t>https://m.place.naver.com/place/1236035000</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>애블바디PT 초롱꽃마을 2호점 헬스PT</t>
+          <t>1퍼센트짐 금릉점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>every_body_pt@naver.com</t>
+          <t>1percentgym2@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1427-5294</t>
+          <t>0507-1386-4598</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 파주시 양지로 117 304호,305호</t>
+          <t>경기 파주시 금빛로 4-1 3층 301호,302호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/</t>
+          <t>https://booking.naver.com/booking/6/bizes/1113882</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1376,7 +1368,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1391,7 +1383,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wdljl0j</t>
+          <t>https://talk.naver.com/ct/w5yr9z</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,17 +1393,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>387</v>
       </c>
       <c r="Q10" t="n">
-        <v>33</v>
+        <v>267</v>
       </c>
       <c r="R10" t="n">
-        <v>36</v>
+        <v>654</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,56 +1412,56 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2038397745</t>
+          <t>1714420485</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2038397745</t>
+          <t>https://m.place.naver.com/place/1714420485</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>애블바디PT 해오름마을 1호점 헬스PT</t>
+          <t>에스엠짐 파주본점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>every_body_pt@naver.com</t>
+          <t>spyangel2@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1362-5290</t>
+          <t>0507-1370-4147</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 파주시 해올2길 16 공감빌딩 6층 애블바디 P.T샵</t>
+          <t>경기 파주시 교하로 957 1, 2층 에스엠짐</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/</t>
+          <t>https://blog.naver.com/spyangel2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1479,19 +1471,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w44dez</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1499,17 +1487,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>148</v>
+        <v>114</v>
       </c>
       <c r="Q11" t="n">
-        <v>277</v>
+        <v>1430</v>
       </c>
       <c r="R11" t="n">
-        <v>425</v>
+        <v>1544</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,17 +1506,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1831911897</t>
+          <t>1184875775</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1831911897</t>
+          <t>https://m.place.naver.com/place/1184875775</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/파주_헬스장.xlsx
+++ b/naver-place-crawler/results_health/파주_헬스장.xlsx
@@ -591,7 +591,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -777,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 파주시 초롱꽃로 141 B동 7층</t>
+          <t>경기 파주시 초롱꽃로 141 B동 7층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -802,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5t0nq</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -820,10 +824,10 @@
         <v>697</v>
       </c>
       <c r="Q4" t="n">
-        <v>1284</v>
+        <v>1304</v>
       </c>
       <c r="R4" t="n">
-        <v>1981</v>
+        <v>2001</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -918,10 +922,10 @@
         <v>894</v>
       </c>
       <c r="Q5" t="n">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="R5" t="n">
-        <v>1464</v>
+        <v>1468</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1067,7 +1071,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 파주시 경의로 1068 삼융프라자 4층 403~4호</t>
+          <t>경기 파주시 경의로 1068 삼융프라자 4층 403~4호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1092,10 +1096,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wphkbsb</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>O</t>
@@ -1110,10 +1118,10 @@
         <v>202</v>
       </c>
       <c r="Q7" t="n">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="R7" t="n">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1161,7 +1169,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 파주시 와석순환로 86 지앤지프라자 5층</t>
+          <t>경기 파주시 와석순환로 86 지앤지프라자 5층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1186,10 +1194,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5itt3</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
